--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
+    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan (Aktualisierung aller enthaltenen Ressourcen) und besteht aus: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus 
-- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
+- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung
+Alle neuen bzw. geänderten und zu entfernenden Medikationsplaneinträge müssen inline im Bundle enthalten sein, alle unveränderten Ressourcen werden referenziert.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan-persistierung-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
